--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_23-10-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_23-10-2025.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£33.29</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£33.29</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£39.70</t>
+          <t>£39.45</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£39.70</t>
+          <t>£39.45</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.63</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.63</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
